--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:18:04+00:00</t>
+    <t>2024-03-21T10:58:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:58:03+00:00</t>
+    <t>2024-03-21T10:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:59:21+00:00</t>
+    <t>2024-03-21T12:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:49:37+00:00</t>
+    <t>2024-03-21T12:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:55:50+00:00</t>
+    <t>2024-03-22T10:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T10:25:22+00:00</t>
+    <t>2024-03-22T13:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T13:38:23+00:00</t>
+    <t>2024-03-25T10:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
